--- a/Task 2/02_c_LAB301x_VN_v0.01_OPPM_Plan_Template.xlsx
+++ b/Task 2/02_c_LAB301x_VN_v0.01_OPPM_Plan_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/working_company/2020_smartpro_planning_skills/_goLIVE/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kohaku\Downloads\LAB301\Task 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEAEFF8-B551-744D-B701-4F9A875C5C88}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B79D8F-C000-4A78-99AE-328D79A7A00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="38400" windowHeight="20040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="2" r:id="rId1"/>
@@ -30,10 +30,29 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={3486CE5B-0EEB-4ADC-B63E-BB85D4F28BAC}</author>
+    <author>tc={216EE87A-CE1B-41F5-8655-E24D6D9DB930}</author>
     <author>Microsoft Office User</author>
   </authors>
   <commentList>
-    <comment ref="J60" authorId="0" shapeId="0" xr:uid="{F90B73BB-1F15-CD43-AECB-A57B7C17353B}">
+    <comment ref="O13" authorId="0" shapeId="0" xr:uid="{3486CE5B-0EEB-4ADC-B63E-BB85D4F28BAC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This is basically just a buffer for func 1 2 3 since we are not doing func 4</t>
+      </text>
+    </comment>
+    <comment ref="Y47" authorId="1" shapeId="0" xr:uid="{216EE87A-CE1B-41F5-8655-E24D6D9DB930}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Do I  need to fill these ?
+</t>
+      </text>
+    </comment>
+    <comment ref="J60" authorId="2" shapeId="0" xr:uid="{F90B73BB-1F15-CD43-AECB-A57B7C17353B}">
       <text>
         <r>
           <rPr>
@@ -71,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
   <si>
     <t>Sub-Objectives</t>
   </si>
@@ -127,58 +146,10 @@
     <t>C</t>
   </si>
   <si>
-    <t>Report Date: 11/12/2019</t>
-  </si>
-  <si>
-    <t>Dev 1</t>
-  </si>
-  <si>
-    <t>Dev 2</t>
-  </si>
-  <si>
-    <t>Dev 3</t>
-  </si>
-  <si>
-    <t>Tester</t>
-  </si>
-  <si>
-    <t>Dev 4</t>
-  </si>
-  <si>
     <t>User Management</t>
   </si>
   <si>
     <t>Role Management</t>
-  </si>
-  <si>
-    <t>Day 1</t>
-  </si>
-  <si>
-    <t>Day 2</t>
-  </si>
-  <si>
-    <t>Day 3</t>
-  </si>
-  <si>
-    <t>Day 4</t>
-  </si>
-  <si>
-    <t>Day 5</t>
-  </si>
-  <si>
-    <t>Day 6</t>
-  </si>
-  <si>
-    <t>Day 7</t>
-  </si>
-  <si>
-    <t>Day 8</t>
-  </si>
-  <si>
-    <t>Day 9</t>
-  </si>
-  <si>
-    <t>Day 10</t>
   </si>
   <si>
     <r>
@@ -253,15 +224,6 @@
     <t>Login Function</t>
   </si>
   <si>
-    <t>Project Name: Build Function of Login, Manage and Authorize Users</t>
-  </si>
-  <si>
-    <t>Project Manager: Nguyen Thanh Phuoc</t>
-  </si>
-  <si>
-    <t>Project Objective: Complete Function of Login, Manage and Authorize Users of the System</t>
-  </si>
-  <si>
     <t>Worrisome</t>
   </si>
   <si>
@@ -269,6 +231,96 @@
   </si>
   <si>
     <t>Dangerous</t>
+  </si>
+  <si>
+    <t>Project Manager: Phan Đặng Duy Phúc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Name:  Ứng dụng Dò Vé Số </t>
+  </si>
+  <si>
+    <t>Report Date: 15/06/2026</t>
+  </si>
+  <si>
+    <t>Project Objective: Xây dựng thành công hệ thống Web quản lý và dò vé số</t>
+  </si>
+  <si>
+    <t>C. Hoàn thiện, Báo cáo &amp; Bảo vệ (Task 9-10).</t>
+  </si>
+  <si>
+    <t>Task 1. Phân tích và xác định yêu cầu</t>
+  </si>
+  <si>
+    <t>Task 2. Lập kế hoạch &amp; quản lý dự án</t>
+  </si>
+  <si>
+    <t>Task 3. Thiết kế kiến trúc &amp; mã nguồn</t>
+  </si>
+  <si>
+    <t>Task 4. Thiết kế CSDL &amp; nhập liệu mẫu</t>
+  </si>
+  <si>
+    <t>Task 5. Xây dựng CN1 - Quản lý người dùng</t>
+  </si>
+  <si>
+    <t>Task 6. Xây dựng CN2 - Quản lý Vé dò</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 7. Xây dựng CN3 - Thực hiện dò vé số </t>
+  </si>
+  <si>
+    <t>Task 8. Tích hợp hệ thống &amp; Kiểm thử</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 9. Viết báo cáo và chuẩn bị bảo vệ </t>
+  </si>
+  <si>
+    <t>Task 10. Bảo vệ dự án</t>
+  </si>
+  <si>
+    <t>08/06 - 14/06</t>
+  </si>
+  <si>
+    <t>15/06 - 21/06</t>
+  </si>
+  <si>
+    <t>22/06 - 28/06</t>
+  </si>
+  <si>
+    <t>29/06 - 05/07</t>
+  </si>
+  <si>
+    <t>06/07 - 12/07</t>
+  </si>
+  <si>
+    <t>13/07 - 19/07</t>
+  </si>
+  <si>
+    <t>20/07 - 26/07</t>
+  </si>
+  <si>
+    <t>27/07 - 02/08</t>
+  </si>
+  <si>
+    <t>02/08 - 09/08</t>
+  </si>
+  <si>
+    <t>Phan Đặng Duy Phúc</t>
+  </si>
+  <si>
+    <t>Not fully understanding the product being created, leading to scope creeping or architecture trailing</t>
+  </si>
+  <si>
+    <t>Not understanding the URD, leading to faulty SRS and faulty product</t>
+  </si>
+  <si>
+    <t>Focusing too much on stuff beyond basic security or design, leading to lack of actual functional requirements implementation</t>
+  </si>
+  <si>
+    <t>Phân tích, Lập kế hoạch &amp; Thiết kế (Task 1-4).</t>
+  </si>
+  <si>
+    <t>Xây dựng Chức năng Hệ thống (Task 5-7).</t>
   </si>
 </sst>
 </file>
@@ -282,7 +334,7 @@
     <numFmt numFmtId="167" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
     <numFmt numFmtId="168" formatCode="_(&quot;$&quot;* #"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -445,6 +497,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -496,7 +554,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="70">
+  <borders count="74">
     <border>
       <left/>
       <right/>
@@ -728,21 +786,6 @@
       </left>
       <right style="hair">
         <color indexed="22"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="22"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
@@ -1100,15 +1143,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -1369,6 +1403,80 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="22"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="22"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1379,168 +1487,145 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="225">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1551,183 +1636,161 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="27"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" textRotation="27"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -1740,12 +1803,12 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1753,31 +1816,30 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -1790,65 +1852,69 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1856,86 +1922,64 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="66" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1943,10 +1987,72 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1955,44 +2061,87 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="17" fontId="4" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="17" fontId="4" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="61" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="62" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2007,140 +2156,98 @@
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="72" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="73" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="17" fontId="4" fillId="8" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="65" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="17" fontId="4" fillId="8" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="68" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2153,17 +2260,11 @@
     <cellStyle name="Normal_Project Matrix" xfId="1" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Normal_Project Matrix Collection II" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="23">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-      </font>
       <fill>
         <patternFill patternType="mediumGray">
-          <fgColor indexed="10"/>
+          <fgColor indexed="51"/>
           <bgColor indexed="9"/>
         </patternFill>
       </fill>
@@ -2171,105 +2272,15 @@
     <dxf>
       <fill>
         <patternFill patternType="mediumGray">
-          <fgColor indexed="42"/>
+          <fgColor indexed="13"/>
           <bgColor indexed="9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="43"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="10"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="42"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="43"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="10"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="42"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="43"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="10"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="42"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="43"/>
+        <patternFill patternType="lightGray">
+          <fgColor indexed="11"/>
           <bgColor indexed="9"/>
         </patternFill>
       </fill>
@@ -2389,25 +2400,15 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+      </font>
       <fill>
         <patternFill patternType="mediumGray">
           <fgColor indexed="10"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="43"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="mediumGray">
-          <fgColor indexed="42"/>
           <bgColor indexed="9"/>
         </patternFill>
       </fill>
@@ -2445,7 +2446,7 @@
     <dxf>
       <fill>
         <patternFill patternType="mediumGray">
-          <fgColor indexed="24"/>
+          <fgColor indexed="10"/>
           <bgColor indexed="9"/>
         </patternFill>
       </fill>
@@ -2453,7 +2454,7 @@
     <dxf>
       <fill>
         <patternFill patternType="mediumGray">
-          <fgColor indexed="51"/>
+          <fgColor indexed="43"/>
           <bgColor indexed="9"/>
         </patternFill>
       </fill>
@@ -2461,15 +2462,15 @@
     <dxf>
       <fill>
         <patternFill patternType="mediumGray">
-          <fgColor indexed="13"/>
+          <fgColor indexed="42"/>
           <bgColor indexed="9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="lightGray">
-          <fgColor indexed="11"/>
+        <patternFill patternType="mediumGray">
+          <fgColor indexed="24"/>
           <bgColor indexed="9"/>
         </patternFill>
       </fill>
@@ -3670,6 +3671,12 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Kohaku" id="{EB96A237-E87F-443C-9291-CBF6B404B456}" userId="Kohaku" providerId="None"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3990,1812 +3997,1849 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="O13" dT="2026-06-15T09:00:51.90" personId="{EB96A237-E87F-443C-9291-CBF6B404B456}" id="{3486CE5B-0EEB-4ADC-B63E-BB85D4F28BAC}">
+    <text>This is basically just a buffer for func 1 2 3 since we are not doing func 4</text>
+  </threadedComment>
+  <threadedComment ref="Y47" dT="2026-06-15T09:01:16.29" personId="{EB96A237-E87F-443C-9291-CBF6B404B456}" id="{216EE87A-CE1B-41F5-8655-E24D6D9DB930}">
+    <text xml:space="preserve">Do I  need to fill these ?
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <dimension ref="B1:AA65"/>
+  <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3" style="2" customWidth="1"/>
-    <col min="2" max="5" width="3.83203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="21.1640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" style="2" customWidth="1"/>
-    <col min="9" max="18" width="5.83203125" style="2" customWidth="1"/>
-    <col min="19" max="22" width="4.83203125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="5.1640625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="3" style="2" customWidth="1"/>
-    <col min="25" max="25" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="10.1640625" style="2"/>
+    <col min="1" max="1" width="3" style="1" customWidth="1"/>
+    <col min="2" max="5" width="3.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" style="1" customWidth="1"/>
+    <col min="9" max="18" width="5.875" style="1" customWidth="1"/>
+    <col min="19" max="22" width="4.875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="5.125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="3" style="1" customWidth="1"/>
+    <col min="25" max="25" width="15.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="10.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1"/>
-    </row>
-    <row r="2" spans="1:27" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="B2" s="6"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="199" t="s">
+    <row r="1" spans="2:27" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:27" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="146" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="145" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="145"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="131" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+    </row>
+    <row r="3" spans="2:27" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="14"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="161" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
+      <c r="M3" s="162"/>
+      <c r="N3" s="162"/>
+      <c r="O3" s="162"/>
+      <c r="P3" s="162"/>
+      <c r="Q3" s="162"/>
+      <c r="R3" s="162"/>
+      <c r="S3" s="162"/>
+      <c r="T3" s="162"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="162"/>
+      <c r="W3" s="163"/>
+      <c r="Y3" s="12"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+    </row>
+    <row r="4" spans="2:27" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="164"/>
+      <c r="F4" s="165"/>
+      <c r="G4" s="165"/>
+      <c r="H4" s="165"/>
+      <c r="I4" s="165"/>
+      <c r="J4" s="165"/>
+      <c r="K4" s="165"/>
+      <c r="L4" s="165"/>
+      <c r="M4" s="165"/>
+      <c r="N4" s="165"/>
+      <c r="O4" s="165"/>
+      <c r="P4" s="165"/>
+      <c r="Q4" s="165"/>
+      <c r="R4" s="165"/>
+      <c r="S4" s="165"/>
+      <c r="T4" s="165"/>
+      <c r="U4" s="165"/>
+      <c r="V4" s="165"/>
+      <c r="W4" s="166"/>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+    </row>
+    <row r="5" spans="2:27" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="167" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="168"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="170" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="171"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="171"/>
+      <c r="O5" s="171"/>
+      <c r="P5" s="171"/>
+      <c r="Q5" s="171"/>
+      <c r="R5" s="172"/>
+      <c r="S5" s="170" t="s">
+        <v>3</v>
+      </c>
+      <c r="T5" s="171"/>
+      <c r="U5" s="171"/>
+      <c r="V5" s="172"/>
+      <c r="W5" s="173"/>
+    </row>
+    <row r="6" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="25"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="112" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="114">
+        <v>1</v>
+      </c>
+      <c r="F6" s="197" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="185"/>
+      <c r="H6" s="186"/>
+      <c r="I6" s="112" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="206" t="s">
+        <v>15</v>
+      </c>
+      <c r="T6" s="126"/>
+      <c r="U6" s="133"/>
+      <c r="V6" s="134"/>
+      <c r="W6" s="135"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
+    </row>
+    <row r="7" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="25"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="112" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="125">
+        <v>2</v>
+      </c>
+      <c r="F7" s="198" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="187"/>
+      <c r="H7" s="188"/>
+      <c r="I7" s="137"/>
+      <c r="J7" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="T7" s="126"/>
+      <c r="U7" s="116"/>
+      <c r="V7" s="116"/>
+      <c r="W7" s="151"/>
+      <c r="Y7" s="28"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+    </row>
+    <row r="8" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="25"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="115">
+        <v>3</v>
+      </c>
+      <c r="F8" s="198" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="187"/>
+      <c r="H8" s="188"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="33"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="207" t="s">
+        <v>15</v>
+      </c>
+      <c r="U8" s="116"/>
+      <c r="V8" s="116"/>
+      <c r="W8" s="117"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="29"/>
+    </row>
+    <row r="9" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="25"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="115">
+        <v>4</v>
+      </c>
+      <c r="F9" s="198" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="187"/>
+      <c r="H9" s="188"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="37"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="33"/>
+      <c r="S9" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="T9" s="116"/>
+      <c r="U9" s="116"/>
+      <c r="V9" s="116"/>
+      <c r="W9" s="151"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+    </row>
+    <row r="10" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="25"/>
+      <c r="C10" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="31"/>
+      <c r="E10" s="115">
+        <v>5</v>
+      </c>
+      <c r="F10" s="198" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="187"/>
+      <c r="H10" s="188"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="36"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="207" t="s">
+        <v>15</v>
+      </c>
+      <c r="T10" s="116"/>
+      <c r="V10" s="116"/>
+      <c r="W10" s="117"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="29"/>
+    </row>
+    <row r="11" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="25"/>
+      <c r="C11" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="31"/>
+      <c r="E11" s="115">
+        <v>6</v>
+      </c>
+      <c r="F11" s="198" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="187"/>
+      <c r="H11" s="188"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="T11" s="116"/>
+      <c r="U11" s="116"/>
+      <c r="V11" s="116"/>
+      <c r="W11" s="151"/>
+      <c r="Y11" s="28"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="29"/>
+    </row>
+    <row r="12" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="25"/>
+      <c r="C12" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="31"/>
+      <c r="E12" s="115">
+        <v>7</v>
+      </c>
+      <c r="F12" s="198" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="187"/>
+      <c r="H12" s="188"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="T12" s="153"/>
+      <c r="U12" s="116"/>
+      <c r="V12" s="116"/>
+      <c r="W12" s="117"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="29"/>
+      <c r="AA12" s="29"/>
+    </row>
+    <row r="13" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="115">
+        <v>8</v>
+      </c>
+      <c r="F13" s="198" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="187"/>
+      <c r="H13" s="188"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="T13" s="116"/>
+      <c r="U13" s="116"/>
+      <c r="V13" s="116"/>
+      <c r="W13" s="151"/>
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
+    </row>
+    <row r="14" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="30"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="115">
+        <v>9</v>
+      </c>
+      <c r="F14" s="198" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="187"/>
+      <c r="H14" s="188"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="T14" s="153"/>
+      <c r="U14" s="116"/>
+      <c r="V14" s="116"/>
+      <c r="W14" s="151"/>
+      <c r="Y14" s="28"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29"/>
+    </row>
+    <row r="15" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="30"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="115">
+        <v>10</v>
+      </c>
+      <c r="F15" s="198" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="167" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="167"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="151" t="s">
+      <c r="G15" s="187"/>
+      <c r="H15" s="188"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="R15" s="33"/>
+      <c r="S15" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="T15" s="116"/>
+      <c r="U15" s="116"/>
+      <c r="V15" s="116"/>
+      <c r="W15" s="151"/>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="29"/>
+    </row>
+    <row r="16" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="25"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="115">
+        <v>11</v>
+      </c>
+      <c r="F16" s="198"/>
+      <c r="G16" s="187"/>
+      <c r="H16" s="188"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="118"/>
+      <c r="T16" s="153"/>
+      <c r="U16" s="116"/>
+      <c r="V16" s="116"/>
+      <c r="W16" s="117"/>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="29"/>
+      <c r="AA16" s="29"/>
+    </row>
+    <row r="17" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="25"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="115">
+        <v>12</v>
+      </c>
+      <c r="F17" s="198"/>
+      <c r="G17" s="187"/>
+      <c r="H17" s="188"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="118"/>
+      <c r="T17" s="116"/>
+      <c r="U17" s="116"/>
+      <c r="V17" s="116"/>
+      <c r="W17" s="151"/>
+      <c r="Y17" s="28"/>
+      <c r="Z17" s="29"/>
+      <c r="AA17" s="29"/>
+    </row>
+    <row r="18" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="25"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="115">
+        <v>13</v>
+      </c>
+      <c r="F18" s="198"/>
+      <c r="G18" s="187"/>
+      <c r="H18" s="188"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="118"/>
+      <c r="U18" s="153"/>
+      <c r="V18" s="116"/>
+      <c r="W18" s="117"/>
+      <c r="Y18" s="28"/>
+      <c r="Z18" s="29"/>
+      <c r="AA18" s="29"/>
+    </row>
+    <row r="19" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="25"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="115">
+        <v>14</v>
+      </c>
+      <c r="F19" s="198"/>
+      <c r="G19" s="187"/>
+      <c r="H19" s="188"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="118"/>
+      <c r="T19" s="116"/>
+      <c r="U19" s="116"/>
+      <c r="V19" s="116"/>
+      <c r="W19" s="151"/>
+      <c r="Y19" s="28"/>
+      <c r="Z19" s="29"/>
+      <c r="AA19" s="29"/>
+    </row>
+    <row r="20" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="25"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="115">
+        <v>15</v>
+      </c>
+      <c r="F20" s="198"/>
+      <c r="G20" s="187"/>
+      <c r="H20" s="188"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="33"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="118"/>
+      <c r="T20" s="116"/>
+      <c r="U20" s="153"/>
+      <c r="V20" s="116"/>
+      <c r="W20" s="117"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="29"/>
+      <c r="AA20" s="29"/>
+    </row>
+    <row r="21" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="25"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="115">
+        <v>16</v>
+      </c>
+      <c r="F21" s="198"/>
+      <c r="G21" s="187"/>
+      <c r="H21" s="188"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="118"/>
+      <c r="T21" s="116"/>
+      <c r="U21" s="116"/>
+      <c r="V21" s="116"/>
+      <c r="W21" s="151"/>
+      <c r="Y21" s="28"/>
+      <c r="Z21" s="29"/>
+      <c r="AA21" s="29"/>
+    </row>
+    <row r="22" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="25"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="115">
+        <v>17</v>
+      </c>
+      <c r="F22" s="198"/>
+      <c r="G22" s="187"/>
+      <c r="H22" s="188"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="118"/>
+      <c r="T22" s="116"/>
+      <c r="U22" s="153"/>
+      <c r="V22" s="116"/>
+      <c r="W22" s="117"/>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="29"/>
+      <c r="AA22" s="29"/>
+    </row>
+    <row r="23" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="25"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="115">
         <v>18</v>
       </c>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-    </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="15"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="200" t="s">
+      <c r="F23" s="198"/>
+      <c r="G23" s="187"/>
+      <c r="H23" s="188"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="33"/>
+      <c r="S23" s="118"/>
+      <c r="T23" s="116"/>
+      <c r="U23" s="116"/>
+      <c r="V23" s="116"/>
+      <c r="W23" s="151"/>
+      <c r="Y23" s="28"/>
+      <c r="Z23" s="29"/>
+      <c r="AA23" s="29"/>
+    </row>
+    <row r="24" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="25"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="115">
+        <v>19</v>
+      </c>
+      <c r="F24" s="198"/>
+      <c r="G24" s="187"/>
+      <c r="H24" s="188"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="33"/>
+      <c r="S24" s="118"/>
+      <c r="T24" s="116"/>
+      <c r="V24" s="153"/>
+      <c r="W24" s="117"/>
+      <c r="Y24" s="28"/>
+      <c r="Z24" s="29"/>
+      <c r="AA24" s="29"/>
+    </row>
+    <row r="25" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="25"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="115">
+        <v>20</v>
+      </c>
+      <c r="F25" s="198"/>
+      <c r="G25" s="187"/>
+      <c r="H25" s="188"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="138"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
+      <c r="S25" s="118"/>
+      <c r="T25" s="116"/>
+      <c r="U25" s="116"/>
+      <c r="V25" s="116"/>
+      <c r="W25" s="151"/>
+      <c r="Y25" s="28"/>
+      <c r="Z25" s="29"/>
+      <c r="AA25" s="29"/>
+    </row>
+    <row r="26" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="25"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="115">
+        <v>21</v>
+      </c>
+      <c r="F26" s="198"/>
+      <c r="G26" s="187"/>
+      <c r="H26" s="188"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="33"/>
+      <c r="S26" s="118"/>
+      <c r="T26" s="116"/>
+      <c r="V26" s="153"/>
+      <c r="W26" s="117"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="29"/>
+      <c r="AA26" s="29"/>
+    </row>
+    <row r="27" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="25"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="115">
+        <v>22</v>
+      </c>
+      <c r="F27" s="198"/>
+      <c r="G27" s="187"/>
+      <c r="H27" s="188"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="139"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="120"/>
+      <c r="T27" s="116"/>
+      <c r="U27" s="116"/>
+      <c r="V27" s="116"/>
+      <c r="W27" s="151"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="29"/>
+      <c r="AA27" s="29"/>
+    </row>
+    <row r="28" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="25"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="115">
+        <v>23</v>
+      </c>
+      <c r="F28" s="198"/>
+      <c r="G28" s="187"/>
+      <c r="H28" s="188"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="R28" s="33"/>
+      <c r="S28" s="118"/>
+      <c r="T28" s="116"/>
+      <c r="V28" s="153"/>
+      <c r="W28" s="117"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="29"/>
+      <c r="AA28" s="29"/>
+    </row>
+    <row r="29" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="39"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="140">
+        <v>24</v>
+      </c>
+      <c r="F29" s="198"/>
+      <c r="G29" s="187"/>
+      <c r="H29" s="188"/>
+      <c r="I29" s="141"/>
+      <c r="J29" s="34"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="34"/>
+      <c r="S29" s="120"/>
+      <c r="T29" s="121"/>
+      <c r="U29" s="121"/>
+      <c r="V29" s="116"/>
+      <c r="W29" s="151"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="29"/>
+      <c r="AA29" s="29"/>
+    </row>
+    <row r="30" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="39"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="140">
+        <v>25</v>
+      </c>
+      <c r="F30" s="198"/>
+      <c r="G30" s="187"/>
+      <c r="H30" s="188"/>
+      <c r="I30" s="141"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="120"/>
+      <c r="T30" s="121"/>
+      <c r="U30" s="121"/>
+      <c r="V30" s="121"/>
+      <c r="W30" s="151"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="29"/>
+      <c r="AA30" s="29"/>
+    </row>
+    <row r="31" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="39"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="195"/>
+      <c r="G31" s="196"/>
+      <c r="H31" s="196"/>
+      <c r="I31" s="141"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="120"/>
+      <c r="T31" s="121"/>
+      <c r="U31" s="121"/>
+      <c r="V31" s="121"/>
+      <c r="W31" s="117"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="29"/>
+      <c r="AA31" s="29"/>
+    </row>
+    <row r="32" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="45"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="136" t="s">
+        <v>20</v>
+      </c>
+      <c r="N32" s="52"/>
+      <c r="O32" s="122"/>
+      <c r="P32" s="52"/>
+      <c r="Q32" s="52"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="123"/>
+      <c r="T32" s="122"/>
+      <c r="U32" s="122"/>
+      <c r="V32" s="127"/>
+      <c r="W32" s="124"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="29"/>
+      <c r="AA32" s="29"/>
+    </row>
+    <row r="33" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="53"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="125">
+        <v>1</v>
+      </c>
+      <c r="F33" s="210" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="211"/>
+      <c r="H33" s="212"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="57"/>
+      <c r="P33" s="57"/>
+      <c r="Q33" s="57"/>
+      <c r="R33" s="57"/>
+      <c r="S33" s="154"/>
+      <c r="T33" s="116"/>
+      <c r="U33" s="153"/>
+      <c r="V33" s="116"/>
+      <c r="W33" s="155"/>
+      <c r="Y33" s="28"/>
+      <c r="Z33" s="29"/>
+      <c r="AA33" s="29"/>
+    </row>
+    <row r="34" spans="2:27" s="24" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="53"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="125">
+        <v>2</v>
+      </c>
+      <c r="F34" s="213" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" s="214"/>
+      <c r="H34" s="215"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="57"/>
+      <c r="O34" s="57"/>
+      <c r="P34" s="57"/>
+      <c r="Q34" s="57"/>
+      <c r="R34" s="143"/>
+      <c r="S34" s="156"/>
+      <c r="T34" s="116"/>
+      <c r="U34" s="153"/>
+      <c r="V34" s="157"/>
+      <c r="W34" s="155"/>
+      <c r="Y34" s="28"/>
+      <c r="Z34" s="29"/>
+      <c r="AA34" s="29"/>
+    </row>
+    <row r="35" spans="2:27" s="24" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="25"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="115">
+        <v>3</v>
+      </c>
+      <c r="F35" s="216" t="s">
+        <v>55</v>
+      </c>
+      <c r="G35" s="217"/>
+      <c r="H35" s="218"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="59"/>
+      <c r="M35" s="59"/>
+      <c r="N35" s="59"/>
+      <c r="O35" s="59"/>
+      <c r="P35" s="59"/>
+      <c r="Q35" s="59"/>
+      <c r="R35" s="59"/>
+      <c r="S35" s="118"/>
+      <c r="T35" s="158"/>
+      <c r="U35" s="116"/>
+      <c r="V35" s="153"/>
+      <c r="W35" s="159"/>
+      <c r="Y35" s="28"/>
+      <c r="Z35" s="29"/>
+      <c r="AA35" s="29"/>
+    </row>
+    <row r="36" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="25"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="115">
+        <v>4</v>
+      </c>
+      <c r="F36" s="213"/>
+      <c r="G36" s="214"/>
+      <c r="H36" s="215"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="59"/>
+      <c r="K36" s="59"/>
+      <c r="L36" s="59"/>
+      <c r="M36" s="59"/>
+      <c r="N36" s="59"/>
+      <c r="O36" s="59"/>
+      <c r="P36" s="59"/>
+      <c r="Q36" s="59"/>
+      <c r="R36" s="60"/>
+      <c r="S36" s="118"/>
+      <c r="T36" s="153"/>
+      <c r="U36" s="116"/>
+      <c r="V36" s="160"/>
+      <c r="W36" s="151"/>
+      <c r="Y36" s="28"/>
+      <c r="Z36" s="29"/>
+      <c r="AA36" s="29"/>
+    </row>
+    <row r="37" spans="2:27" s="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="25"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="115">
+        <v>5</v>
+      </c>
+      <c r="F37" s="213"/>
+      <c r="G37" s="214"/>
+      <c r="H37" s="215"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="59"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="59"/>
+      <c r="M37" s="59"/>
+      <c r="N37" s="59"/>
+      <c r="O37" s="59"/>
+      <c r="P37" s="59"/>
+      <c r="Q37" s="59"/>
+      <c r="R37" s="59"/>
+      <c r="S37" s="152"/>
+      <c r="T37" s="116"/>
+      <c r="U37" s="116"/>
+      <c r="V37" s="116"/>
+      <c r="W37" s="117"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="29"/>
+      <c r="AA37" s="29"/>
+    </row>
+    <row r="38" spans="2:27" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="61"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="65"/>
+      <c r="O38" s="65"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="65"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="66"/>
+      <c r="T38" s="67"/>
+      <c r="U38" s="67"/>
+      <c r="V38" s="128"/>
+      <c r="W38" s="68"/>
+      <c r="Y38" s="28"/>
+      <c r="Z38" s="29"/>
+      <c r="AA38" s="29"/>
+    </row>
+    <row r="39" spans="2:27" s="24" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="69"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="72"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="74"/>
+      <c r="H39" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="I39" s="76"/>
+      <c r="J39" s="77"/>
+      <c r="K39" s="77"/>
+      <c r="L39" s="77"/>
+      <c r="M39" s="77"/>
+      <c r="N39" s="77"/>
+      <c r="O39" s="77"/>
+      <c r="P39" s="77"/>
+      <c r="Q39" s="77"/>
+      <c r="R39" s="77"/>
+      <c r="S39" s="76"/>
+      <c r="T39" s="77"/>
+      <c r="U39" s="77"/>
+      <c r="V39" s="129"/>
+      <c r="W39" s="78"/>
+      <c r="Y39" s="28"/>
+      <c r="Z39" s="29"/>
+      <c r="AA39" s="29"/>
+    </row>
+    <row r="40" spans="2:27" s="24" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="79"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
+      <c r="I40" s="84"/>
+      <c r="J40" s="85"/>
+      <c r="K40" s="85"/>
+      <c r="L40" s="85"/>
+      <c r="M40" s="85"/>
+      <c r="N40" s="85"/>
+      <c r="O40" s="85"/>
+      <c r="P40" s="85"/>
+      <c r="Q40" s="85"/>
+      <c r="R40" s="85"/>
+      <c r="S40" s="84"/>
+      <c r="T40" s="85"/>
+      <c r="U40" s="85"/>
+      <c r="V40" s="130"/>
+      <c r="W40" s="86"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="29"/>
+      <c r="AA40" s="29"/>
+    </row>
+    <row r="41" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="201" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="201" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="202" t="s">
+        <v>56</v>
+      </c>
+      <c r="F41" s="87"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="208" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="201"/>
-      <c r="G3" s="201"/>
-      <c r="H3" s="201"/>
-      <c r="I3" s="201"/>
-      <c r="J3" s="201"/>
-      <c r="K3" s="201"/>
-      <c r="L3" s="201"/>
-      <c r="M3" s="201"/>
-      <c r="N3" s="201"/>
-      <c r="O3" s="201"/>
-      <c r="P3" s="201"/>
-      <c r="Q3" s="201"/>
-      <c r="R3" s="201"/>
-      <c r="S3" s="201"/>
-      <c r="T3" s="201"/>
-      <c r="U3" s="201"/>
-      <c r="V3" s="201"/>
-      <c r="W3" s="202"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-    </row>
-    <row r="4" spans="1:27" s="18" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="19"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="203"/>
-      <c r="F4" s="204"/>
-      <c r="G4" s="204"/>
-      <c r="H4" s="204"/>
-      <c r="I4" s="204"/>
-      <c r="J4" s="204"/>
-      <c r="K4" s="204"/>
-      <c r="L4" s="204"/>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="204"/>
-      <c r="W4" s="205"/>
-      <c r="Y4" s="21"/>
-      <c r="Z4" s="22"/>
-      <c r="AA4" s="22"/>
-    </row>
-    <row r="5" spans="1:27" s="1" customFormat="1" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="168" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="169"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="171" t="s">
-        <v>2</v>
-      </c>
-      <c r="J5" s="172"/>
-      <c r="K5" s="172"/>
-      <c r="L5" s="172"/>
-      <c r="M5" s="172"/>
-      <c r="N5" s="172"/>
-      <c r="O5" s="172"/>
-      <c r="P5" s="172"/>
-      <c r="Q5" s="172"/>
-      <c r="R5" s="173"/>
-      <c r="S5" s="171" t="s">
-        <v>3</v>
-      </c>
-      <c r="T5" s="172"/>
-      <c r="U5" s="172"/>
-      <c r="V5" s="173"/>
-      <c r="W5" s="174"/>
-      <c r="Y5" s="26"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="27"/>
-    </row>
-    <row r="6" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="29"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="131">
-        <v>1</v>
-      </c>
-      <c r="F6" s="133"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="213"/>
-      <c r="T6" s="146"/>
-      <c r="U6" s="153"/>
-      <c r="V6" s="154"/>
-      <c r="W6" s="155"/>
-      <c r="Y6" s="35"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="36"/>
-    </row>
-    <row r="7" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="29"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="144">
-        <v>2</v>
-      </c>
-      <c r="F7" s="206"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="158"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="136"/>
-      <c r="T7" s="146"/>
-      <c r="U7" s="134"/>
-      <c r="V7" s="134"/>
-      <c r="W7" s="214"/>
-      <c r="Y7" s="35"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="36"/>
-    </row>
-    <row r="8" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="29"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="132">
-        <v>3</v>
-      </c>
-      <c r="F8" s="133"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="41"/>
-      <c r="S8" s="215"/>
-      <c r="T8" s="216"/>
-      <c r="U8" s="134"/>
-      <c r="V8" s="134"/>
-      <c r="W8" s="135"/>
-      <c r="Y8" s="35"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="36"/>
-    </row>
-    <row r="9" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="29"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="132">
-        <v>4</v>
-      </c>
-      <c r="F9" s="133"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="136"/>
-      <c r="T9" s="134"/>
-      <c r="U9" s="134"/>
-      <c r="V9" s="134"/>
-      <c r="W9" s="214"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="36"/>
-    </row>
-    <row r="10" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="29"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="132">
-        <v>5</v>
-      </c>
-      <c r="F10" s="133"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="215"/>
-      <c r="T10" s="134"/>
-      <c r="U10" s="216"/>
-      <c r="V10" s="134"/>
-      <c r="W10" s="135"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="36"/>
-      <c r="AA10" s="36"/>
-    </row>
-    <row r="11" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="29"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="132">
+      <c r="J41" s="174" t="s">
+        <v>44</v>
+      </c>
+      <c r="K41" s="174" t="s">
+        <v>45</v>
+      </c>
+      <c r="L41" s="174" t="s">
+        <v>46</v>
+      </c>
+      <c r="M41" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N41" s="199" t="s">
+        <v>48</v>
+      </c>
+      <c r="O41" s="199" t="s">
+        <v>49</v>
+      </c>
+      <c r="P41" s="199" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q41" s="199" t="s">
+        <v>51</v>
+      </c>
+      <c r="R41" s="199"/>
+      <c r="S41" s="178" t="s">
+        <v>52</v>
+      </c>
+      <c r="T41" s="181"/>
+      <c r="U41" s="181"/>
+      <c r="V41" s="181"/>
+      <c r="W41" s="192"/>
+      <c r="Y41" s="28"/>
+      <c r="Z41" s="29"/>
+      <c r="AA41" s="29"/>
+    </row>
+    <row r="42" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="203"/>
+      <c r="C42" s="203"/>
+      <c r="D42" s="202"/>
+      <c r="F42" s="89"/>
+      <c r="G42" s="88"/>
+      <c r="H42" s="88"/>
+      <c r="I42" s="208"/>
+      <c r="J42" s="174"/>
+      <c r="K42" s="174"/>
+      <c r="L42" s="174"/>
+      <c r="M42" s="174"/>
+      <c r="N42" s="199"/>
+      <c r="O42" s="199"/>
+      <c r="P42" s="199"/>
+      <c r="Q42" s="199"/>
+      <c r="R42" s="199"/>
+      <c r="S42" s="179"/>
+      <c r="T42" s="182"/>
+      <c r="U42" s="182"/>
+      <c r="V42" s="181"/>
+      <c r="W42" s="193"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="29"/>
+      <c r="AA42" s="29"/>
+    </row>
+    <row r="43" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="203"/>
+      <c r="C43" s="203"/>
+      <c r="D43" s="202"/>
+      <c r="F43" s="89"/>
+      <c r="G43" s="88"/>
+      <c r="H43" s="88"/>
+      <c r="I43" s="208"/>
+      <c r="J43" s="174"/>
+      <c r="K43" s="174"/>
+      <c r="L43" s="174"/>
+      <c r="M43" s="174"/>
+      <c r="N43" s="199"/>
+      <c r="O43" s="199"/>
+      <c r="P43" s="199"/>
+      <c r="Q43" s="199"/>
+      <c r="R43" s="199"/>
+      <c r="S43" s="179"/>
+      <c r="T43" s="182"/>
+      <c r="U43" s="182"/>
+      <c r="V43" s="181"/>
+      <c r="W43" s="193"/>
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="29"/>
+      <c r="AA43" s="29"/>
+    </row>
+    <row r="44" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="203"/>
+      <c r="C44" s="203"/>
+      <c r="D44" s="202"/>
+      <c r="F44" s="90"/>
+      <c r="G44" s="88"/>
+      <c r="H44" s="88"/>
+      <c r="I44" s="208"/>
+      <c r="J44" s="174"/>
+      <c r="K44" s="174"/>
+      <c r="L44" s="174"/>
+      <c r="M44" s="174"/>
+      <c r="N44" s="199"/>
+      <c r="O44" s="199"/>
+      <c r="P44" s="199"/>
+      <c r="Q44" s="199"/>
+      <c r="R44" s="199"/>
+      <c r="S44" s="179"/>
+      <c r="T44" s="182"/>
+      <c r="U44" s="182"/>
+      <c r="V44" s="181"/>
+      <c r="W44" s="193"/>
+      <c r="Z44" s="29"/>
+      <c r="AA44" s="29"/>
+    </row>
+    <row r="45" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="203"/>
+      <c r="C45" s="203"/>
+      <c r="D45" s="202"/>
+      <c r="F45" s="87"/>
+      <c r="G45" s="88"/>
+      <c r="H45" s="88"/>
+      <c r="I45" s="208"/>
+      <c r="J45" s="174"/>
+      <c r="K45" s="174"/>
+      <c r="L45" s="174"/>
+      <c r="M45" s="174"/>
+      <c r="N45" s="199"/>
+      <c r="O45" s="199"/>
+      <c r="P45" s="199"/>
+      <c r="Q45" s="199"/>
+      <c r="R45" s="199"/>
+      <c r="S45" s="179"/>
+      <c r="T45" s="182"/>
+      <c r="U45" s="182"/>
+      <c r="V45" s="181"/>
+      <c r="W45" s="193"/>
+      <c r="Z45" s="29"/>
+      <c r="AA45" s="29"/>
+    </row>
+    <row r="46" spans="2:27" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="203"/>
+      <c r="C46" s="203"/>
+      <c r="D46" s="202"/>
+      <c r="F46" s="91"/>
+      <c r="G46" s="88"/>
+      <c r="H46" s="88"/>
+      <c r="I46" s="209"/>
+      <c r="J46" s="175"/>
+      <c r="K46" s="175"/>
+      <c r="L46" s="175"/>
+      <c r="M46" s="175"/>
+      <c r="N46" s="200"/>
+      <c r="O46" s="200"/>
+      <c r="P46" s="200"/>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="200"/>
+      <c r="S46" s="180"/>
+      <c r="T46" s="183"/>
+      <c r="U46" s="183"/>
+      <c r="V46" s="191"/>
+      <c r="W46" s="194"/>
+      <c r="Z46" s="2"/>
+      <c r="AA46" s="2"/>
+    </row>
+    <row r="47" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="203"/>
+      <c r="C47" s="203"/>
+      <c r="D47" s="202"/>
+      <c r="F47" s="91"/>
+      <c r="G47" s="91"/>
+      <c r="H47" s="91"/>
+      <c r="I47" s="92"/>
+      <c r="J47" s="93"/>
+      <c r="K47" s="93"/>
+      <c r="L47" s="93"/>
+      <c r="M47" s="93"/>
+      <c r="N47" s="93"/>
+      <c r="O47" s="93"/>
+      <c r="P47" s="93"/>
+      <c r="Q47" s="93"/>
+      <c r="R47" s="93"/>
+      <c r="S47" s="93"/>
+      <c r="T47" s="93"/>
+      <c r="U47" s="93"/>
+      <c r="V47" s="93"/>
+      <c r="W47" s="94"/>
+      <c r="Z47" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="133"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="41"/>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="41"/>
-      <c r="S11" s="136"/>
-      <c r="T11" s="134"/>
-      <c r="U11" s="134"/>
-      <c r="V11" s="134"/>
-      <c r="W11" s="214"/>
-      <c r="Y11" s="35"/>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="36"/>
-    </row>
-    <row r="12" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="29"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="132">
+      <c r="AA47" s="184"/>
+    </row>
+    <row r="48" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="203"/>
+      <c r="C48" s="203"/>
+      <c r="D48" s="202"/>
+      <c r="E48" s="95"/>
+      <c r="F48" s="91"/>
+      <c r="G48" s="89"/>
+      <c r="H48" s="89"/>
+      <c r="I48" s="96"/>
+      <c r="J48" s="97"/>
+      <c r="K48" s="97"/>
+      <c r="L48" s="97"/>
+      <c r="M48" s="97"/>
+      <c r="N48" s="97"/>
+      <c r="O48" s="97"/>
+      <c r="P48" s="97"/>
+      <c r="Q48" s="97"/>
+      <c r="R48" s="97"/>
+      <c r="S48" s="97"/>
+      <c r="T48" s="97"/>
+      <c r="U48" s="97"/>
+      <c r="V48" s="97"/>
+      <c r="W48" s="98"/>
+      <c r="Y48" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="133"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="41"/>
-      <c r="S12" s="136"/>
-      <c r="T12" s="217"/>
-      <c r="U12" s="134"/>
-      <c r="V12" s="134"/>
-      <c r="W12" s="135"/>
-      <c r="Y12" s="35"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="36"/>
-    </row>
-    <row r="13" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="29"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="132">
+      <c r="Z48" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="133"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="45"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="41"/>
-      <c r="S13" s="136"/>
-      <c r="T13" s="134"/>
-      <c r="U13" s="134"/>
-      <c r="V13" s="134"/>
-      <c r="W13" s="214"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="36"/>
-    </row>
-    <row r="14" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="29"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="132">
+      <c r="AA48" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="133"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="136"/>
-      <c r="T14" s="217"/>
-      <c r="U14" s="134"/>
-      <c r="V14" s="134"/>
-      <c r="W14" s="214"/>
-      <c r="Y14" s="35"/>
-      <c r="Z14" s="36"/>
-      <c r="AA14" s="36"/>
-    </row>
-    <row r="15" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="29"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="132">
+    </row>
+    <row r="49" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="203"/>
+      <c r="C49" s="203"/>
+      <c r="D49" s="202"/>
+      <c r="F49" s="87"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="89"/>
+      <c r="I49" s="96"/>
+      <c r="J49" s="97"/>
+      <c r="K49" s="97"/>
+      <c r="L49" s="97"/>
+      <c r="M49" s="97"/>
+      <c r="N49" s="97"/>
+      <c r="O49" s="97"/>
+      <c r="P49" s="97"/>
+      <c r="Q49" s="97"/>
+      <c r="R49" s="97"/>
+      <c r="S49" s="97"/>
+      <c r="T49" s="97"/>
+      <c r="U49" s="97"/>
+      <c r="V49" s="97"/>
+      <c r="W49" s="98"/>
+      <c r="Y49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z49" s="144"/>
+      <c r="AA49" s="101"/>
+    </row>
+    <row r="50" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B50" s="203"/>
+      <c r="C50" s="203"/>
+      <c r="D50" s="202"/>
+      <c r="F50" s="87"/>
+      <c r="G50" s="89"/>
+      <c r="H50" s="102"/>
+      <c r="I50" s="96"/>
+      <c r="J50" s="97"/>
+      <c r="K50" s="97"/>
+      <c r="L50" s="97"/>
+      <c r="M50" s="97"/>
+      <c r="N50" s="97"/>
+      <c r="O50" s="97"/>
+      <c r="P50" s="97"/>
+      <c r="Q50" s="97"/>
+      <c r="R50" s="97"/>
+      <c r="S50" s="97"/>
+      <c r="T50" s="97"/>
+      <c r="U50" s="97"/>
+      <c r="V50" s="97"/>
+      <c r="W50" s="98"/>
+      <c r="Y50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z50" s="144"/>
+      <c r="AA50" s="103"/>
+    </row>
+    <row r="51" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="203"/>
+      <c r="C51" s="203"/>
+      <c r="D51" s="202"/>
+      <c r="F51" s="87"/>
+      <c r="G51" s="87"/>
+      <c r="H51" s="87"/>
+      <c r="I51" s="96"/>
+      <c r="J51" s="97"/>
+      <c r="K51" s="97"/>
+      <c r="L51" s="97"/>
+      <c r="M51" s="97"/>
+      <c r="N51" s="97"/>
+      <c r="O51" s="97"/>
+      <c r="P51" s="97"/>
+      <c r="Q51" s="97"/>
+      <c r="R51" s="97"/>
+      <c r="S51" s="97"/>
+      <c r="T51" s="97"/>
+      <c r="U51" s="97"/>
+      <c r="V51" s="97"/>
+      <c r="W51" s="98"/>
+      <c r="Y51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z51" s="144"/>
+      <c r="AA51" s="101"/>
+    </row>
+    <row r="52" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B52" s="203"/>
+      <c r="C52" s="203"/>
+      <c r="D52" s="202"/>
+      <c r="F52" s="104"/>
+      <c r="I52" s="96"/>
+      <c r="J52" s="97"/>
+      <c r="K52" s="97"/>
+      <c r="L52" s="97"/>
+      <c r="M52" s="97"/>
+      <c r="N52" s="97"/>
+      <c r="O52" s="97"/>
+      <c r="P52" s="97"/>
+      <c r="Q52" s="97"/>
+      <c r="R52" s="97"/>
+      <c r="S52" s="97"/>
+      <c r="T52" s="97"/>
+      <c r="U52" s="97"/>
+      <c r="V52" s="97"/>
+      <c r="W52" s="98"/>
+      <c r="Z52" s="105"/>
+    </row>
+    <row r="53" spans="2:27" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="203"/>
+      <c r="C53" s="203"/>
+      <c r="D53" s="202"/>
+      <c r="E53" s="106"/>
+      <c r="F53" s="106"/>
+      <c r="G53" s="106"/>
+      <c r="H53" s="106"/>
+      <c r="I53" s="107"/>
+      <c r="J53" s="108"/>
+      <c r="K53" s="108"/>
+      <c r="L53" s="108"/>
+      <c r="M53" s="108"/>
+      <c r="N53" s="108"/>
+      <c r="O53" s="108"/>
+      <c r="P53" s="108"/>
+      <c r="Q53" s="108"/>
+      <c r="R53" s="108"/>
+      <c r="S53" s="108"/>
+      <c r="T53" s="108"/>
+      <c r="U53" s="108"/>
+      <c r="V53" s="108"/>
+      <c r="W53" s="109"/>
+      <c r="Z53" s="105"/>
+      <c r="AA53" s="105"/>
+    </row>
+    <row r="54" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="203"/>
+      <c r="C54" s="203"/>
+      <c r="D54" s="202"/>
+      <c r="E54" s="185"/>
+      <c r="F54" s="185"/>
+      <c r="G54" s="185"/>
+      <c r="H54" s="185"/>
+      <c r="I54" s="185"/>
+      <c r="J54" s="185"/>
+      <c r="K54" s="185"/>
+      <c r="L54" s="185"/>
+      <c r="M54" s="185"/>
+      <c r="N54" s="185"/>
+      <c r="O54" s="185"/>
+      <c r="P54" s="185"/>
+      <c r="Q54" s="185"/>
+      <c r="R54" s="185"/>
+      <c r="S54" s="185"/>
+      <c r="T54" s="185"/>
+      <c r="U54" s="185"/>
+      <c r="V54" s="185"/>
+      <c r="W54" s="186"/>
+    </row>
+    <row r="55" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="203"/>
+      <c r="C55" s="203"/>
+      <c r="D55" s="202"/>
+      <c r="E55" s="187"/>
+      <c r="F55" s="187"/>
+      <c r="G55" s="187"/>
+      <c r="H55" s="187"/>
+      <c r="I55" s="187"/>
+      <c r="J55" s="187"/>
+      <c r="K55" s="187"/>
+      <c r="L55" s="187"/>
+      <c r="M55" s="187"/>
+      <c r="N55" s="187"/>
+      <c r="O55" s="187"/>
+      <c r="P55" s="187"/>
+      <c r="Q55" s="187"/>
+      <c r="R55" s="187"/>
+      <c r="S55" s="187"/>
+      <c r="T55" s="187"/>
+      <c r="U55" s="187"/>
+      <c r="V55" s="187"/>
+      <c r="W55" s="188"/>
+    </row>
+    <row r="56" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="203"/>
+      <c r="C56" s="203"/>
+      <c r="D56" s="202"/>
+      <c r="E56" s="187"/>
+      <c r="F56" s="187"/>
+      <c r="G56" s="187"/>
+      <c r="H56" s="187"/>
+      <c r="I56" s="187"/>
+      <c r="J56" s="187"/>
+      <c r="K56" s="187"/>
+      <c r="L56" s="187"/>
+      <c r="M56" s="187"/>
+      <c r="N56" s="187"/>
+      <c r="O56" s="187"/>
+      <c r="P56" s="187"/>
+      <c r="Q56" s="187"/>
+      <c r="R56" s="187"/>
+      <c r="S56" s="187"/>
+      <c r="T56" s="187"/>
+      <c r="U56" s="187"/>
+      <c r="V56" s="187"/>
+      <c r="W56" s="188"/>
+    </row>
+    <row r="57" spans="2:27" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="204"/>
+      <c r="C57" s="204"/>
+      <c r="D57" s="205"/>
+      <c r="E57" s="176"/>
+      <c r="F57" s="176"/>
+      <c r="G57" s="176"/>
+      <c r="H57" s="176"/>
+      <c r="I57" s="176"/>
+      <c r="J57" s="176"/>
+      <c r="K57" s="176"/>
+      <c r="L57" s="176"/>
+      <c r="M57" s="176"/>
+      <c r="N57" s="176"/>
+      <c r="O57" s="176"/>
+      <c r="P57" s="176"/>
+      <c r="Q57" s="176"/>
+      <c r="R57" s="176"/>
+      <c r="S57" s="176"/>
+      <c r="T57" s="176"/>
+      <c r="U57" s="176"/>
+      <c r="V57" s="176"/>
+      <c r="W57" s="177"/>
+    </row>
+    <row r="59" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="K59" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="L59" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="133"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="41"/>
-      <c r="S15" s="136"/>
-      <c r="T15" s="134"/>
-      <c r="U15" s="134"/>
-      <c r="V15" s="134"/>
-      <c r="W15" s="214"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="36"/>
-      <c r="AA15" s="36"/>
-    </row>
-    <row r="16" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="29"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="132">
+      <c r="M59" s="110" t="s">
+        <v>13</v>
+      </c>
+      <c r="N59" s="110" t="s">
+        <v>12</v>
+      </c>
+      <c r="O59" s="111"/>
+      <c r="P59" s="111"/>
+      <c r="Q59" s="111"/>
+      <c r="R59" s="111"/>
+      <c r="S59" s="119" t="s">
+        <v>15</v>
+      </c>
+      <c r="T59" s="189" t="s">
+        <v>21</v>
+      </c>
+      <c r="U59" s="190"/>
+      <c r="V59" s="111"/>
+      <c r="W59" s="111"/>
+      <c r="X59" s="111"/>
+      <c r="Y59" s="111"/>
+      <c r="Z59" s="111"/>
+      <c r="AA59" s="111"/>
+    </row>
+    <row r="60" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="J60" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K60" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="133"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="136"/>
-      <c r="T16" s="217"/>
-      <c r="U16" s="134"/>
-      <c r="V16" s="134"/>
-      <c r="W16" s="135"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="36"/>
-      <c r="AA16" s="36"/>
-    </row>
-    <row r="17" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="29"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="132">
+      <c r="L60" s="112" t="s">
+        <v>10</v>
+      </c>
+      <c r="M60" s="112" t="s">
+        <v>13</v>
+      </c>
+      <c r="N60" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="133"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="136"/>
-      <c r="T17" s="134"/>
-      <c r="U17" s="134"/>
-      <c r="V17" s="134"/>
-      <c r="W17" s="214"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="36"/>
-      <c r="AA17" s="36"/>
-    </row>
-    <row r="18" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="29"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="132">
-        <v>13</v>
-      </c>
-      <c r="F18" s="133"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="41"/>
-      <c r="S18" s="136"/>
-      <c r="T18" s="216"/>
-      <c r="U18" s="217"/>
-      <c r="V18" s="134"/>
-      <c r="W18" s="135"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="36"/>
-    </row>
-    <row r="19" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="29"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="132">
-        <v>14</v>
-      </c>
-      <c r="F19" s="133"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="41"/>
-      <c r="S19" s="136"/>
-      <c r="T19" s="134"/>
-      <c r="U19" s="134"/>
-      <c r="V19" s="134"/>
-      <c r="W19" s="214"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="36"/>
-      <c r="AA19" s="36"/>
-    </row>
-    <row r="20" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="29"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="132">
-        <v>15</v>
-      </c>
-      <c r="F20" s="133"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="41"/>
-      <c r="M20" s="41"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="41"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="41"/>
-      <c r="S20" s="136"/>
-      <c r="T20" s="134"/>
-      <c r="U20" s="217"/>
-      <c r="V20" s="134"/>
-      <c r="W20" s="135"/>
-      <c r="Y20" s="35"/>
-      <c r="Z20" s="36"/>
-      <c r="AA20" s="36"/>
-    </row>
-    <row r="21" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="29"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="132">
+      <c r="O60" s="113"/>
+      <c r="P60" s="113"/>
+      <c r="Q60" s="113"/>
+      <c r="R60" s="113"/>
+      <c r="S60" s="132" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="133"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="41"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="41"/>
-      <c r="S21" s="136"/>
-      <c r="T21" s="134"/>
-      <c r="U21" s="134"/>
-      <c r="V21" s="134"/>
-      <c r="W21" s="214"/>
-      <c r="Y21" s="35"/>
-      <c r="Z21" s="36"/>
-      <c r="AA21" s="36"/>
-    </row>
-    <row r="22" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="29"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="132">
+      <c r="T60" s="189" t="s">
+        <v>22</v>
+      </c>
+      <c r="U60" s="190"/>
+      <c r="V60" s="113"/>
+      <c r="W60" s="113"/>
+      <c r="X60" s="113"/>
+      <c r="Y60" s="113"/>
+      <c r="Z60" s="113"/>
+      <c r="AA60" s="113"/>
+    </row>
+    <row r="61" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="S61" s="142" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="133"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="41"/>
-      <c r="L22" s="41"/>
-      <c r="M22" s="41"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="41"/>
-      <c r="P22" s="41"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="41"/>
-      <c r="S22" s="136"/>
-      <c r="T22" s="134"/>
-      <c r="U22" s="217"/>
-      <c r="V22" s="134"/>
-      <c r="W22" s="135"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="36"/>
-      <c r="AA22" s="36"/>
-    </row>
-    <row r="23" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="29"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="132">
-        <v>18</v>
-      </c>
-      <c r="F23" s="133"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="41"/>
-      <c r="M23" s="41"/>
-      <c r="N23" s="41"/>
-      <c r="O23" s="41"/>
-      <c r="P23" s="41"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="41"/>
-      <c r="S23" s="136"/>
-      <c r="T23" s="134"/>
-      <c r="U23" s="134"/>
-      <c r="V23" s="134"/>
-      <c r="W23" s="214"/>
-      <c r="Y23" s="35"/>
-      <c r="Z23" s="36"/>
-      <c r="AA23" s="36"/>
-    </row>
-    <row r="24" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="29"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="132">
-        <v>19</v>
-      </c>
-      <c r="F24" s="133"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="41"/>
-      <c r="S24" s="136"/>
-      <c r="T24" s="134"/>
-      <c r="U24" s="216"/>
-      <c r="V24" s="217"/>
-      <c r="W24" s="135"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="36"/>
-      <c r="AA24" s="36"/>
-    </row>
-    <row r="25" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="29"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="132">
-        <v>20</v>
-      </c>
-      <c r="F25" s="133"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="159"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="41"/>
-      <c r="S25" s="136"/>
-      <c r="T25" s="134"/>
-      <c r="U25" s="134"/>
-      <c r="V25" s="134"/>
-      <c r="W25" s="214"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="36"/>
-      <c r="AA25" s="36"/>
-    </row>
-    <row r="26" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="29"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="132">
-        <v>21</v>
-      </c>
-      <c r="F26" s="133"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="41"/>
-      <c r="S26" s="136"/>
-      <c r="T26" s="134"/>
-      <c r="U26" s="216"/>
-      <c r="V26" s="217"/>
-      <c r="W26" s="135"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="36"/>
-      <c r="AA26" s="36"/>
-    </row>
-    <row r="27" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="29"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="132">
-        <v>22</v>
-      </c>
-      <c r="F27" s="133"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="160"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="41"/>
-      <c r="S27" s="139"/>
-      <c r="T27" s="134"/>
-      <c r="U27" s="134"/>
-      <c r="V27" s="134"/>
-      <c r="W27" s="214"/>
-      <c r="Y27" s="35"/>
-      <c r="Z27" s="36"/>
-      <c r="AA27" s="36"/>
-    </row>
-    <row r="28" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="29"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="132">
+      <c r="T61" s="189" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="133"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="41"/>
-      <c r="R28" s="41"/>
-      <c r="S28" s="136"/>
-      <c r="T28" s="134"/>
-      <c r="U28" s="216"/>
-      <c r="V28" s="217"/>
-      <c r="W28" s="135"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="36"/>
-      <c r="AA28" s="36"/>
-    </row>
-    <row r="29" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="48"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="161">
-        <v>24</v>
-      </c>
-      <c r="F29" s="133"/>
-      <c r="G29" s="162"/>
-      <c r="H29" s="162"/>
-      <c r="I29" s="163"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="42"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="42"/>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="42"/>
-      <c r="S29" s="139"/>
-      <c r="T29" s="140"/>
-      <c r="U29" s="140"/>
-      <c r="V29" s="134"/>
-      <c r="W29" s="214"/>
-      <c r="Y29" s="35"/>
-      <c r="Z29" s="36"/>
-      <c r="AA29" s="36"/>
-    </row>
-    <row r="30" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="48"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="161">
-        <v>25</v>
-      </c>
-      <c r="F30" s="133"/>
-      <c r="G30" s="162"/>
-      <c r="H30" s="162"/>
-      <c r="I30" s="163"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="139"/>
-      <c r="T30" s="140"/>
-      <c r="U30" s="140"/>
-      <c r="V30" s="140"/>
-      <c r="W30" s="214"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="36"/>
-      <c r="AA30" s="36"/>
-    </row>
-    <row r="31" spans="2:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="48"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="161"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="162"/>
-      <c r="H31" s="162"/>
-      <c r="I31" s="163"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="42"/>
-      <c r="R31" s="42"/>
-      <c r="S31" s="139"/>
-      <c r="T31" s="140"/>
-      <c r="U31" s="140"/>
-      <c r="V31" s="140"/>
-      <c r="W31" s="135"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="36"/>
-      <c r="AA31" s="36"/>
-    </row>
-    <row r="32" spans="2:27" s="28" customFormat="1" ht="14" x14ac:dyDescent="0.2">
-      <c r="B32" s="54"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="156" t="s">
-        <v>36</v>
-      </c>
-      <c r="N32" s="61"/>
-      <c r="O32" s="141"/>
-      <c r="P32" s="61"/>
-      <c r="Q32" s="61"/>
-      <c r="R32" s="61"/>
-      <c r="S32" s="142"/>
-      <c r="T32" s="141"/>
-      <c r="U32" s="141"/>
-      <c r="V32" s="147"/>
-      <c r="W32" s="143"/>
-      <c r="Y32" s="35"/>
-      <c r="Z32" s="36"/>
-      <c r="AA32" s="36"/>
-    </row>
-    <row r="33" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="62"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="144">
-        <v>1</v>
-      </c>
-      <c r="F33" s="145"/>
-      <c r="G33" s="65"/>
-      <c r="H33" s="65"/>
-      <c r="I33" s="66"/>
-      <c r="J33" s="67"/>
-      <c r="K33" s="67"/>
-      <c r="L33" s="67"/>
-      <c r="M33" s="67"/>
-      <c r="N33" s="67"/>
-      <c r="O33" s="67"/>
-      <c r="P33" s="67"/>
-      <c r="Q33" s="67"/>
-      <c r="R33" s="67"/>
-      <c r="S33" s="218"/>
-      <c r="T33" s="134"/>
-      <c r="U33" s="217"/>
-      <c r="V33" s="134"/>
-      <c r="W33" s="219"/>
-      <c r="Y33" s="35"/>
-      <c r="Z33" s="36"/>
-      <c r="AA33" s="36"/>
-    </row>
-    <row r="34" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="62"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="144">
-        <v>2</v>
-      </c>
-      <c r="F34" s="145"/>
-      <c r="G34" s="65"/>
-      <c r="H34" s="65"/>
-      <c r="I34" s="66"/>
-      <c r="J34" s="67"/>
-      <c r="K34" s="67"/>
-      <c r="L34" s="67"/>
-      <c r="M34" s="67"/>
-      <c r="N34" s="67"/>
-      <c r="O34" s="67"/>
-      <c r="P34" s="67"/>
-      <c r="Q34" s="67"/>
-      <c r="R34" s="165"/>
-      <c r="S34" s="220"/>
-      <c r="T34" s="134"/>
-      <c r="U34" s="217"/>
-      <c r="V34" s="221"/>
-      <c r="W34" s="219"/>
-      <c r="Y34" s="35"/>
-      <c r="Z34" s="36"/>
-      <c r="AA34" s="36"/>
-    </row>
-    <row r="35" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="29"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="132">
-        <v>3</v>
-      </c>
-      <c r="F35" s="138"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="69"/>
-      <c r="L35" s="69"/>
-      <c r="M35" s="69"/>
-      <c r="N35" s="69"/>
-      <c r="O35" s="69"/>
-      <c r="P35" s="69"/>
-      <c r="Q35" s="69"/>
-      <c r="R35" s="69"/>
-      <c r="S35" s="136"/>
-      <c r="T35" s="222"/>
-      <c r="U35" s="134"/>
-      <c r="V35" s="217"/>
-      <c r="W35" s="223"/>
-      <c r="Y35" s="35"/>
-      <c r="Z35" s="36"/>
-      <c r="AA35" s="36"/>
-    </row>
-    <row r="36" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="29"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="132">
-        <v>4</v>
-      </c>
-      <c r="F36" s="138"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="68"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="69"/>
-      <c r="L36" s="69"/>
-      <c r="M36" s="69"/>
-      <c r="N36" s="69"/>
-      <c r="O36" s="69"/>
-      <c r="P36" s="69"/>
-      <c r="Q36" s="69"/>
-      <c r="R36" s="70"/>
-      <c r="S36" s="136"/>
-      <c r="T36" s="217"/>
-      <c r="U36" s="134"/>
-      <c r="V36" s="224"/>
-      <c r="W36" s="214"/>
-      <c r="Y36" s="35"/>
-      <c r="Z36" s="36"/>
-      <c r="AA36" s="36"/>
-    </row>
-    <row r="37" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="29"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="132">
-        <v>5</v>
-      </c>
-      <c r="F37" s="138"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="46"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="69"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="69"/>
-      <c r="P37" s="69"/>
-      <c r="Q37" s="69"/>
-      <c r="R37" s="69"/>
-      <c r="S37" s="215"/>
-      <c r="T37" s="134"/>
-      <c r="U37" s="134"/>
-      <c r="V37" s="134"/>
-      <c r="W37" s="135"/>
-      <c r="Y37" s="35"/>
-      <c r="Z37" s="36"/>
-      <c r="AA37" s="36"/>
-    </row>
-    <row r="38" spans="1:27" s="28" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="71"/>
-      <c r="C38" s="72"/>
-      <c r="D38" s="73"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="53"/>
-      <c r="I38" s="74"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="75"/>
-      <c r="L38" s="75"/>
-      <c r="M38" s="75"/>
-      <c r="N38" s="75"/>
-      <c r="O38" s="75"/>
-      <c r="P38" s="75"/>
-      <c r="Q38" s="75"/>
-      <c r="R38" s="75"/>
-      <c r="S38" s="76"/>
-      <c r="T38" s="77"/>
-      <c r="U38" s="77"/>
-      <c r="V38" s="148"/>
-      <c r="W38" s="78"/>
-      <c r="Y38" s="35"/>
-      <c r="Z38" s="36"/>
-      <c r="AA38" s="36"/>
-    </row>
-    <row r="39" spans="1:27" s="90" customFormat="1" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="79"/>
-      <c r="B39" s="80"/>
-      <c r="C39" s="81"/>
-      <c r="D39" s="82"/>
-      <c r="E39" s="83"/>
-      <c r="F39" s="84"/>
-      <c r="G39" s="85"/>
-      <c r="H39" s="86" t="s">
-        <v>5</v>
-      </c>
-      <c r="I39" s="87"/>
-      <c r="J39" s="88"/>
-      <c r="K39" s="88"/>
-      <c r="L39" s="88"/>
-      <c r="M39" s="88"/>
-      <c r="N39" s="88"/>
-      <c r="O39" s="88"/>
-      <c r="P39" s="88"/>
-      <c r="Q39" s="88"/>
-      <c r="R39" s="88"/>
-      <c r="S39" s="87"/>
-      <c r="T39" s="88"/>
-      <c r="U39" s="88"/>
-      <c r="V39" s="149"/>
-      <c r="W39" s="89"/>
-      <c r="Y39" s="91"/>
-      <c r="Z39" s="92"/>
-      <c r="AA39" s="92"/>
-    </row>
-    <row r="40" spans="1:27" s="28" customFormat="1" ht="5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="93"/>
-      <c r="C40" s="94"/>
-      <c r="D40" s="95"/>
-      <c r="E40" s="96"/>
-      <c r="F40" s="97"/>
-      <c r="G40" s="97"/>
-      <c r="H40" s="97"/>
-      <c r="I40" s="98"/>
-      <c r="J40" s="99"/>
-      <c r="K40" s="99"/>
-      <c r="L40" s="99"/>
-      <c r="M40" s="99"/>
-      <c r="N40" s="99"/>
-      <c r="O40" s="99"/>
-      <c r="P40" s="99"/>
-      <c r="Q40" s="99"/>
-      <c r="R40" s="99"/>
-      <c r="S40" s="98"/>
-      <c r="T40" s="99"/>
-      <c r="U40" s="99"/>
-      <c r="V40" s="150"/>
-      <c r="W40" s="100"/>
-      <c r="X40" s="2"/>
-      <c r="Y40" s="35"/>
-      <c r="Z40" s="36"/>
-      <c r="AA40" s="36"/>
-    </row>
-    <row r="41" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="175"/>
-      <c r="C41" s="175"/>
-      <c r="D41" s="207"/>
-      <c r="E41" s="106"/>
-      <c r="F41" s="101"/>
-      <c r="G41" s="102"/>
-      <c r="H41" s="102"/>
-      <c r="I41" s="178" t="s">
-        <v>26</v>
-      </c>
-      <c r="J41" s="178" t="s">
-        <v>27</v>
-      </c>
-      <c r="K41" s="178" t="s">
-        <v>28</v>
-      </c>
-      <c r="L41" s="178" t="s">
-        <v>29</v>
-      </c>
-      <c r="M41" s="178" t="s">
-        <v>30</v>
-      </c>
-      <c r="N41" s="178" t="s">
-        <v>31</v>
-      </c>
-      <c r="O41" s="178" t="s">
-        <v>32</v>
-      </c>
-      <c r="P41" s="178" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q41" s="178" t="s">
-        <v>34</v>
-      </c>
-      <c r="R41" s="178" t="s">
-        <v>35</v>
-      </c>
-      <c r="S41" s="182" t="s">
-        <v>19</v>
-      </c>
-      <c r="T41" s="185" t="s">
-        <v>20</v>
-      </c>
-      <c r="U41" s="185" t="s">
-        <v>21</v>
-      </c>
-      <c r="V41" s="185" t="s">
-        <v>23</v>
-      </c>
-      <c r="W41" s="196" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y41" s="35"/>
-      <c r="Z41" s="36"/>
-      <c r="AA41" s="36"/>
-    </row>
-    <row r="42" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="176"/>
-      <c r="C42" s="176"/>
-      <c r="D42" s="207"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="103"/>
-      <c r="G42" s="102"/>
-      <c r="H42" s="102"/>
-      <c r="I42" s="178"/>
-      <c r="J42" s="178"/>
-      <c r="K42" s="178"/>
-      <c r="L42" s="178"/>
-      <c r="M42" s="178"/>
-      <c r="N42" s="178"/>
-      <c r="O42" s="178"/>
-      <c r="P42" s="178"/>
-      <c r="Q42" s="178"/>
-      <c r="R42" s="178"/>
-      <c r="S42" s="183"/>
-      <c r="T42" s="186"/>
-      <c r="U42" s="186"/>
-      <c r="V42" s="185"/>
-      <c r="W42" s="197"/>
-      <c r="Y42" s="35"/>
-      <c r="Z42" s="36"/>
-      <c r="AA42" s="36"/>
-    </row>
-    <row r="43" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="176"/>
-      <c r="C43" s="176"/>
-      <c r="D43" s="207"/>
-      <c r="E43" s="106"/>
-      <c r="F43" s="103"/>
-      <c r="G43" s="102"/>
-      <c r="H43" s="102"/>
-      <c r="I43" s="178"/>
-      <c r="J43" s="178"/>
-      <c r="K43" s="178"/>
-      <c r="L43" s="178"/>
-      <c r="M43" s="178"/>
-      <c r="N43" s="178"/>
-      <c r="O43" s="178"/>
-      <c r="P43" s="178"/>
-      <c r="Q43" s="178"/>
-      <c r="R43" s="178"/>
-      <c r="S43" s="183"/>
-      <c r="T43" s="186"/>
-      <c r="U43" s="186"/>
-      <c r="V43" s="185"/>
-      <c r="W43" s="197"/>
-      <c r="Y43" s="35"/>
-      <c r="Z43" s="36"/>
-      <c r="AA43" s="36"/>
-    </row>
-    <row r="44" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="176"/>
-      <c r="C44" s="176"/>
-      <c r="D44" s="207"/>
-      <c r="E44" s="106"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="102"/>
-      <c r="H44" s="102"/>
-      <c r="I44" s="178"/>
-      <c r="J44" s="178"/>
-      <c r="K44" s="178"/>
-      <c r="L44" s="178"/>
-      <c r="M44" s="178"/>
-      <c r="N44" s="178"/>
-      <c r="O44" s="178"/>
-      <c r="P44" s="178"/>
-      <c r="Q44" s="178"/>
-      <c r="R44" s="178"/>
-      <c r="S44" s="183"/>
-      <c r="T44" s="186"/>
-      <c r="U44" s="186"/>
-      <c r="V44" s="185"/>
-      <c r="W44" s="197"/>
-      <c r="Z44" s="36"/>
-      <c r="AA44" s="36"/>
-    </row>
-    <row r="45" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B45" s="176"/>
-      <c r="C45" s="176"/>
-      <c r="D45" s="207"/>
-      <c r="E45" s="106"/>
-      <c r="F45" s="101"/>
-      <c r="G45" s="102"/>
-      <c r="H45" s="102"/>
-      <c r="I45" s="178"/>
-      <c r="J45" s="178"/>
-      <c r="K45" s="178"/>
-      <c r="L45" s="178"/>
-      <c r="M45" s="178"/>
-      <c r="N45" s="178"/>
-      <c r="O45" s="178"/>
-      <c r="P45" s="178"/>
-      <c r="Q45" s="178"/>
-      <c r="R45" s="178"/>
-      <c r="S45" s="183"/>
-      <c r="T45" s="186"/>
-      <c r="U45" s="186"/>
-      <c r="V45" s="185"/>
-      <c r="W45" s="197"/>
-      <c r="Z45" s="36"/>
-      <c r="AA45" s="36"/>
-    </row>
-    <row r="46" spans="1:27" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="176"/>
-      <c r="C46" s="176"/>
-      <c r="D46" s="207"/>
-      <c r="E46" s="106"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="102"/>
-      <c r="H46" s="102"/>
-      <c r="I46" s="179"/>
-      <c r="J46" s="179"/>
-      <c r="K46" s="179"/>
-      <c r="L46" s="179"/>
-      <c r="M46" s="179"/>
-      <c r="N46" s="179"/>
-      <c r="O46" s="179"/>
-      <c r="P46" s="179"/>
-      <c r="Q46" s="179"/>
-      <c r="R46" s="179"/>
-      <c r="S46" s="184"/>
-      <c r="T46" s="187"/>
-      <c r="U46" s="187"/>
-      <c r="V46" s="195"/>
-      <c r="W46" s="198"/>
-      <c r="Y46" s="26"/>
-      <c r="Z46" s="26"/>
-      <c r="AA46" s="26"/>
-    </row>
-    <row r="47" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B47" s="176"/>
-      <c r="C47" s="176"/>
-      <c r="D47" s="207"/>
-      <c r="E47" s="106"/>
-      <c r="F47" s="105"/>
-      <c r="G47" s="105"/>
-      <c r="H47" s="105"/>
-      <c r="I47" s="107"/>
-      <c r="J47" s="108"/>
-      <c r="K47" s="108"/>
-      <c r="L47" s="108"/>
-      <c r="M47" s="108"/>
-      <c r="N47" s="108"/>
-      <c r="O47" s="108"/>
-      <c r="P47" s="108"/>
-      <c r="Q47" s="108"/>
-      <c r="R47" s="108"/>
-      <c r="S47" s="108"/>
-      <c r="T47" s="108"/>
-      <c r="U47" s="108"/>
-      <c r="V47" s="108"/>
-      <c r="W47" s="109"/>
-      <c r="Y47" s="26"/>
-      <c r="Z47" s="188" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA47" s="188"/>
-    </row>
-    <row r="48" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="176"/>
-      <c r="C48" s="176"/>
-      <c r="D48" s="207"/>
-      <c r="E48" s="110"/>
-      <c r="F48" s="105"/>
-      <c r="G48" s="103"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="111"/>
-      <c r="J48" s="112"/>
-      <c r="K48" s="112"/>
-      <c r="L48" s="112"/>
-      <c r="M48" s="112"/>
-      <c r="N48" s="112"/>
-      <c r="O48" s="112"/>
-      <c r="P48" s="112"/>
-      <c r="Q48" s="112"/>
-      <c r="R48" s="112"/>
-      <c r="S48" s="112"/>
-      <c r="T48" s="112"/>
-      <c r="U48" s="112"/>
-      <c r="V48" s="112"/>
-      <c r="W48" s="113"/>
-      <c r="Y48" s="114" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z48" s="115" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA48" s="115" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="176"/>
-      <c r="C49" s="176"/>
-      <c r="D49" s="207"/>
-      <c r="E49" s="106"/>
-      <c r="F49" s="101"/>
-      <c r="G49" s="103"/>
-      <c r="H49" s="103"/>
-      <c r="I49" s="111"/>
-      <c r="J49" s="112"/>
-      <c r="K49" s="112"/>
-      <c r="L49" s="112"/>
-      <c r="M49" s="112"/>
-      <c r="N49" s="112"/>
-      <c r="O49" s="112"/>
-      <c r="P49" s="112"/>
-      <c r="Q49" s="112"/>
-      <c r="R49" s="112"/>
-      <c r="S49" s="112"/>
-      <c r="T49" s="112"/>
-      <c r="U49" s="112"/>
-      <c r="V49" s="112"/>
-      <c r="W49" s="113"/>
-      <c r="Y49" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z49" s="166"/>
-      <c r="AA49" s="116"/>
-    </row>
-    <row r="50" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B50" s="176"/>
-      <c r="C50" s="176"/>
-      <c r="D50" s="207"/>
-      <c r="E50" s="106"/>
-      <c r="F50" s="101"/>
-      <c r="G50" s="103"/>
-      <c r="H50" s="117"/>
-      <c r="I50" s="111"/>
-      <c r="J50" s="112"/>
-      <c r="K50" s="112"/>
-      <c r="L50" s="112"/>
-      <c r="M50" s="112"/>
-      <c r="N50" s="112"/>
-      <c r="O50" s="112"/>
-      <c r="P50" s="112"/>
-      <c r="Q50" s="112"/>
-      <c r="R50" s="112"/>
-      <c r="S50" s="112"/>
-      <c r="T50" s="112"/>
-      <c r="U50" s="112"/>
-      <c r="V50" s="112"/>
-      <c r="W50" s="113"/>
-      <c r="Y50" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z50" s="166"/>
-      <c r="AA50" s="118"/>
-    </row>
-    <row r="51" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B51" s="176"/>
-      <c r="C51" s="176"/>
-      <c r="D51" s="207"/>
-      <c r="E51" s="106"/>
-      <c r="F51" s="101"/>
-      <c r="G51" s="101"/>
-      <c r="H51" s="101"/>
-      <c r="I51" s="111"/>
-      <c r="J51" s="112"/>
-      <c r="K51" s="112"/>
-      <c r="L51" s="112"/>
-      <c r="M51" s="112"/>
-      <c r="N51" s="112"/>
-      <c r="O51" s="112"/>
-      <c r="P51" s="112"/>
-      <c r="Q51" s="112"/>
-      <c r="R51" s="112"/>
-      <c r="S51" s="112"/>
-      <c r="T51" s="112"/>
-      <c r="U51" s="112"/>
-      <c r="V51" s="112"/>
-      <c r="W51" s="113"/>
-      <c r="Y51" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z51" s="166"/>
-      <c r="AA51" s="116"/>
-    </row>
-    <row r="52" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B52" s="176"/>
-      <c r="C52" s="176"/>
-      <c r="D52" s="207"/>
-      <c r="E52" s="106"/>
-      <c r="F52" s="119"/>
-      <c r="G52" s="106"/>
-      <c r="H52" s="106"/>
-      <c r="I52" s="111"/>
-      <c r="J52" s="112"/>
-      <c r="K52" s="112"/>
-      <c r="L52" s="112"/>
-      <c r="M52" s="112"/>
-      <c r="N52" s="112"/>
-      <c r="O52" s="112"/>
-      <c r="P52" s="112"/>
-      <c r="Q52" s="112"/>
-      <c r="R52" s="112"/>
-      <c r="S52" s="112"/>
-      <c r="T52" s="112"/>
-      <c r="U52" s="112"/>
-      <c r="V52" s="112"/>
-      <c r="W52" s="113"/>
-      <c r="Y52" s="26"/>
-      <c r="Z52" s="120"/>
-    </row>
-    <row r="53" spans="2:27" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="176"/>
-      <c r="C53" s="176"/>
-      <c r="D53" s="207"/>
-      <c r="E53" s="122"/>
-      <c r="F53" s="121"/>
-      <c r="G53" s="122"/>
-      <c r="H53" s="122"/>
-      <c r="I53" s="123"/>
-      <c r="J53" s="124"/>
-      <c r="K53" s="124"/>
-      <c r="L53" s="124"/>
-      <c r="M53" s="124"/>
-      <c r="N53" s="124"/>
-      <c r="O53" s="124"/>
-      <c r="P53" s="124"/>
-      <c r="Q53" s="124"/>
-      <c r="R53" s="124"/>
-      <c r="S53" s="124"/>
-      <c r="T53" s="124"/>
-      <c r="U53" s="124"/>
-      <c r="V53" s="124"/>
-      <c r="W53" s="125"/>
-      <c r="Z53" s="120"/>
-      <c r="AA53" s="120"/>
-    </row>
-    <row r="54" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B54" s="176"/>
-      <c r="C54" s="176"/>
-      <c r="D54" s="207"/>
-      <c r="E54" s="189"/>
-      <c r="F54" s="189"/>
-      <c r="G54" s="189"/>
-      <c r="H54" s="189"/>
-      <c r="I54" s="189"/>
-      <c r="J54" s="189"/>
-      <c r="K54" s="189"/>
-      <c r="L54" s="189"/>
-      <c r="M54" s="189"/>
-      <c r="N54" s="189"/>
-      <c r="O54" s="189"/>
-      <c r="P54" s="189"/>
-      <c r="Q54" s="189"/>
-      <c r="R54" s="189"/>
-      <c r="S54" s="189"/>
-      <c r="T54" s="189"/>
-      <c r="U54" s="189"/>
-      <c r="V54" s="189"/>
-      <c r="W54" s="190"/>
-    </row>
-    <row r="55" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B55" s="176"/>
-      <c r="C55" s="176"/>
-      <c r="D55" s="207"/>
-      <c r="E55" s="191"/>
-      <c r="F55" s="191"/>
-      <c r="G55" s="191"/>
-      <c r="H55" s="191"/>
-      <c r="I55" s="191"/>
-      <c r="J55" s="191"/>
-      <c r="K55" s="191"/>
-      <c r="L55" s="191"/>
-      <c r="M55" s="191"/>
-      <c r="N55" s="191"/>
-      <c r="O55" s="191"/>
-      <c r="P55" s="191"/>
-      <c r="Q55" s="191"/>
-      <c r="R55" s="191"/>
-      <c r="S55" s="191"/>
-      <c r="T55" s="191"/>
-      <c r="U55" s="191"/>
-      <c r="V55" s="191"/>
-      <c r="W55" s="192"/>
-    </row>
-    <row r="56" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B56" s="176"/>
-      <c r="C56" s="176"/>
-      <c r="D56" s="207"/>
-      <c r="E56" s="191"/>
-      <c r="F56" s="191"/>
-      <c r="G56" s="191"/>
-      <c r="H56" s="191"/>
-      <c r="I56" s="191"/>
-      <c r="J56" s="191"/>
-      <c r="K56" s="191"/>
-      <c r="L56" s="191"/>
-      <c r="M56" s="191"/>
-      <c r="N56" s="191"/>
-      <c r="O56" s="191"/>
-      <c r="P56" s="191"/>
-      <c r="Q56" s="191"/>
-      <c r="R56" s="191"/>
-      <c r="S56" s="191"/>
-      <c r="T56" s="191"/>
-      <c r="U56" s="191"/>
-      <c r="V56" s="191"/>
-      <c r="W56" s="192"/>
-    </row>
-    <row r="57" spans="2:27" s="1" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="177"/>
-      <c r="C57" s="177"/>
-      <c r="D57" s="208"/>
-      <c r="E57" s="180"/>
-      <c r="F57" s="180"/>
-      <c r="G57" s="180"/>
-      <c r="H57" s="180"/>
-      <c r="I57" s="180"/>
-      <c r="J57" s="180"/>
-      <c r="K57" s="180"/>
-      <c r="L57" s="180"/>
-      <c r="M57" s="180"/>
-      <c r="N57" s="180"/>
-      <c r="O57" s="180"/>
-      <c r="P57" s="180"/>
-      <c r="Q57" s="180"/>
-      <c r="R57" s="180"/>
-      <c r="S57" s="180"/>
-      <c r="T57" s="180"/>
-      <c r="U57" s="180"/>
-      <c r="V57" s="180"/>
-      <c r="W57" s="181"/>
-      <c r="Y57" s="26"/>
-      <c r="Z57" s="27"/>
-      <c r="AA57" s="27"/>
-    </row>
-    <row r="58" spans="2:27" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="Y58" s="26"/>
-      <c r="Z58" s="27"/>
-      <c r="AA58" s="27"/>
-    </row>
-    <row r="59" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="H59" s="126"/>
-      <c r="I59" s="126"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="127" t="s">
-        <v>11</v>
-      </c>
-      <c r="L59" s="127" t="s">
-        <v>10</v>
-      </c>
-      <c r="M59" s="127" t="s">
-        <v>13</v>
-      </c>
-      <c r="N59" s="127" t="s">
-        <v>12</v>
-      </c>
-      <c r="O59" s="128"/>
-      <c r="P59" s="128"/>
-      <c r="Q59" s="128"/>
-      <c r="R59" s="128"/>
-      <c r="S59" s="137" t="s">
-        <v>15</v>
-      </c>
-      <c r="T59" s="193" t="s">
-        <v>37</v>
-      </c>
-      <c r="U59" s="194"/>
-      <c r="V59" s="128"/>
-      <c r="W59" s="128"/>
-      <c r="X59" s="128"/>
-      <c r="Y59" s="128"/>
-      <c r="Z59" s="128"/>
-      <c r="AA59" s="128"/>
-    </row>
-    <row r="60" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="H60" s="126"/>
-      <c r="I60" s="126"/>
-      <c r="J60" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K60" s="129" t="s">
-        <v>11</v>
-      </c>
-      <c r="L60" s="129" t="s">
-        <v>10</v>
-      </c>
-      <c r="M60" s="129" t="s">
-        <v>13</v>
-      </c>
-      <c r="N60" s="129" t="s">
-        <v>12</v>
-      </c>
-      <c r="O60" s="130"/>
-      <c r="P60" s="130"/>
-      <c r="Q60" s="130"/>
-      <c r="R60" s="130"/>
-      <c r="S60" s="152" t="s">
-        <v>16</v>
-      </c>
-      <c r="T60" s="193" t="s">
-        <v>38</v>
-      </c>
-      <c r="U60" s="194"/>
-      <c r="V60" s="130"/>
-      <c r="W60" s="130"/>
-      <c r="X60" s="130"/>
-      <c r="Y60" s="130"/>
-      <c r="Z60" s="130"/>
-      <c r="AA60" s="130"/>
-    </row>
-    <row r="61" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="126"/>
-      <c r="I61" s="126"/>
-      <c r="J61" s="126"/>
-      <c r="K61" s="126"/>
-      <c r="L61" s="126"/>
-      <c r="M61" s="126"/>
-      <c r="N61" s="126"/>
-      <c r="O61" s="126"/>
-      <c r="P61" s="126"/>
-      <c r="Q61" s="126"/>
-      <c r="R61" s="126"/>
-      <c r="S61" s="164" t="s">
-        <v>17</v>
-      </c>
-      <c r="T61" s="193" t="s">
-        <v>39</v>
-      </c>
-      <c r="U61" s="194"/>
-      <c r="V61" s="126"/>
-      <c r="W61" s="126"/>
-      <c r="X61" s="126"/>
-      <c r="Y61" s="126"/>
-      <c r="Z61" s="126"/>
-      <c r="AA61" s="126"/>
-    </row>
-    <row r="62" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1"/>
-      <c r="S62" s="1"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="1"/>
-      <c r="V62" s="1"/>
-      <c r="W62" s="1"/>
-      <c r="X62" s="1"/>
+      <c r="U61" s="190"/>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
+    </row>
+    <row r="62" spans="2:27" x14ac:dyDescent="0.2">
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
     </row>
-    <row r="63" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="K63" s="209"/>
-      <c r="L63" s="212" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" spans="2:27" x14ac:dyDescent="0.15">
-      <c r="K64" s="210"/>
-      <c r="L64" s="212" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="65" spans="11:12" x14ac:dyDescent="0.15">
-      <c r="K65" s="211"/>
-      <c r="L65" s="212" t="s">
-        <v>46</v>
+    <row r="63" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="K63" s="147"/>
+      <c r="L63" s="150" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="K64" s="148"/>
+      <c r="L64" s="150" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="11:12" x14ac:dyDescent="0.2">
+      <c r="K65" s="149"/>
+      <c r="L65" s="150" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="60">
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F12:H12"/>
     <mergeCell ref="T61:U61"/>
     <mergeCell ref="E56:W56"/>
     <mergeCell ref="U41:U46"/>
@@ -5826,131 +5870,96 @@
     <mergeCell ref="R41:R46"/>
     <mergeCell ref="S41:S46"/>
     <mergeCell ref="T41:T46"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F7:H7"/>
   </mergeCells>
-  <conditionalFormatting sqref="S40:W40">
-    <cfRule type="cellIs" dxfId="33" priority="55" stopIfTrue="1" operator="equal">
-      <formula>"A"</formula>
+  <conditionalFormatting sqref="B40:D40">
+    <cfRule type="cellIs" dxfId="22" priority="58" stopIfTrue="1" operator="notEqual">
+      <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="56" stopIfTrue="1" operator="equal">
-      <formula>"B"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H60:I60 V60:AA60">
+    <cfRule type="cellIs" dxfId="21" priority="62" stopIfTrue="1" operator="equal">
+      <formula>"G"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="57" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="63" stopIfTrue="1" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="64" stopIfTrue="1" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I20:L27 I16:R19 J6:R6 I7:I8 K7:R8 I9:J9 L9:R9 I10:K10 M10:R10 I11:L11 N11:R11 I12:M12 O12:R12 I13:N13 P13:R13 I14:O14 Q14:R14 I15:P15 R15">
+    <cfRule type="cellIs" dxfId="18" priority="49" stopIfTrue="1" operator="equal">
+      <formula>"S"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="50" stopIfTrue="1" operator="equal">
+      <formula>"C"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="51" stopIfTrue="1" operator="equal">
+      <formula>"D"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I30:R39">
+    <cfRule type="cellIs" dxfId="15" priority="12" stopIfTrue="1" operator="equal">
+      <formula>"D"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I30:R40">
+    <cfRule type="cellIs" dxfId="14" priority="10" stopIfTrue="1" operator="equal">
+      <formula>"S"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="11" stopIfTrue="1" operator="equal">
       <formula>"C"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B40:D40">
-    <cfRule type="cellIs" dxfId="30" priority="58" stopIfTrue="1" operator="notEqual">
-      <formula>""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I40:R40">
-    <cfRule type="cellIs" dxfId="29" priority="59" stopIfTrue="1" operator="equal">
-      <formula>"S"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="60" stopIfTrue="1" operator="equal">
-      <formula>"C"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="61" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="61" stopIfTrue="1" operator="equal">
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H60:I60 O60:R60 V60:AA60">
-    <cfRule type="cellIs" dxfId="26" priority="62" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="M20:P25 R20:R29 N26:P27 I28:P28 I29:O29 Q29">
+    <cfRule type="cellIs" dxfId="11" priority="52" stopIfTrue="1" operator="equal">
+      <formula>"S"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="53" stopIfTrue="1" operator="equal">
+      <formula>"C"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="54" stopIfTrue="1" operator="equal">
+      <formula>"D"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M60:R60">
+    <cfRule type="cellIs" dxfId="8" priority="25" stopIfTrue="1" operator="equal">
       <formula>"G"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="63" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="26" stopIfTrue="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="64" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="27" stopIfTrue="1" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I30:R30 N26:P27 R20:R29 M20:P25 I28:P28 I29:O29 Q29 I33:R39">
-    <cfRule type="cellIs" dxfId="23" priority="52" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="Q20:Q27">
+    <cfRule type="cellIs" dxfId="5" priority="1" stopIfTrue="1" operator="equal">
       <formula>"S"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="53" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" stopIfTrue="1" operator="equal">
       <formula>"C"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="54" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" stopIfTrue="1" operator="equal">
       <formula>"D"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:R19 I20:L27">
-    <cfRule type="cellIs" dxfId="20" priority="49" stopIfTrue="1" operator="equal">
-      <formula>"S"</formula>
+  <conditionalFormatting sqref="S40:W40">
+    <cfRule type="cellIs" dxfId="2" priority="55" stopIfTrue="1" operator="equal">
+      <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="50" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="56" stopIfTrue="1" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="57" stopIfTrue="1" operator="equal">
       <formula>"C"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="51" stopIfTrue="1" operator="equal">
-      <formula>"D"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M60:N60">
-    <cfRule type="cellIs" dxfId="17" priority="25" stopIfTrue="1" operator="equal">
-      <formula>"G"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="26" stopIfTrue="1" operator="equal">
-      <formula>"Y"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="27" stopIfTrue="1" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I32:R32">
-    <cfRule type="cellIs" dxfId="14" priority="16" stopIfTrue="1" operator="equal">
-      <formula>"S"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="17" stopIfTrue="1" operator="equal">
-      <formula>"C"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="18" stopIfTrue="1" operator="equal">
-      <formula>"D"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I31:R31">
-    <cfRule type="cellIs" dxfId="11" priority="10" stopIfTrue="1" operator="equal">
-      <formula>"S"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="11" stopIfTrue="1" operator="equal">
-      <formula>"C"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="12" stopIfTrue="1" operator="equal">
-      <formula>"D"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q27">
-    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="equal">
-      <formula>"S"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="equal">
-      <formula>"C"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="equal">
-      <formula>"D"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q20:Q24">
-    <cfRule type="cellIs" dxfId="5" priority="4" stopIfTrue="1" operator="equal">
-      <formula>"S"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" stopIfTrue="1" operator="equal">
-      <formula>"C"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" stopIfTrue="1" operator="equal">
-      <formula>"D"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q25:Q26">
-    <cfRule type="cellIs" dxfId="2" priority="1" stopIfTrue="1" operator="equal">
-      <formula>"S"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="equal">
-      <formula>"C"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" stopIfTrue="1" operator="equal">
-      <formula>"D"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.65" bottom="0.35" header="0.4" footer="0.2"/>
